--- a/output/ai-shinryou-db/text/2026/hosei-tsuuchi-i/2026_様式101・102（歯科技工所）［61KB］_20260501.xlsx
+++ b/output/ai-shinryou-db/text/2026/hosei-tsuuchi-i/2026_様式101・102（歯科技工所）［61KB］_20260501.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mhlwlan.sharepoint.com/sites/12404000/WorkingDocLib/保険局　医療課/03_法令１係/★令和８年度診療報酬改定★/01_タコ部屋関係/30_訂正通知/第２弾/01_担当登録/0413柳三ベア訂正事項（登録用）/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="281" documentId="8_{29614C23-BE0D-4248-99EF-D851CD220BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3953CC16-0D5F-4845-8C28-CCD09E880115}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="8_{29614C23-BE0D-4248-99EF-D851CD220BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5AE8590-1C42-489F-B8EC-A53914D209EE}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="FwOXZuoNYoLgly0oUNDY5Afq+9yfpbEJUEml2qU7y5i/W18VOmsve6kncwIKmjO2lJp6Deun8+Nnq7VQ0/5eHg==" workbookSaltValue="CjqN+dc1ElfIiQQ5fkM3bg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1ED11763-137E-40A5-B093-377CBC27F218}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1ED11763-137E-40A5-B093-377CBC27F218}"/>
   </bookViews>
   <sheets>
     <sheet name="別添2" sheetId="8" r:id="rId1"/>
@@ -2136,6 +2136,62 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
@@ -2169,61 +2225,16 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2243,17 +2254,66 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="12" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2280,69 +2340,9 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="12" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4304,19 +4304,22 @@
     <col min="12" max="13" width="3.625" style="42" customWidth="1"/>
     <col min="14" max="14" width="9.5" style="42" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="15" max="19" width="9" style="42" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="9" style="42" collapsed="1"/>
+    <col min="20" max="20" width="9.5" style="42" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="21" max="16384" width="9" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:20">
       <c r="A1" s="42" t="s">
         <v>110</v>
       </c>
       <c r="M1" s="97">
         <v>202503</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="18.75" customHeight="1">
+      <c r="T1" s="97">
+        <v>20260501</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="18.75" customHeight="1">
       <c r="A3" s="96" t="s">
         <v>109</v>
       </c>
@@ -4333,7 +4336,7 @@
       <c r="L3" s="95"/>
       <c r="M3" s="95"/>
     </row>
-    <row r="4" spans="1:16" ht="11.25" customHeight="1" thickBot="1">
+    <row r="4" spans="1:20" ht="11.25" customHeight="1" thickBot="1">
       <c r="A4" s="96"/>
       <c r="B4" s="95"/>
       <c r="C4" s="95"/>
@@ -4348,7 +4351,7 @@
       <c r="L4" s="95"/>
       <c r="M4" s="95"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:20">
       <c r="A5" s="94"/>
       <c r="B5" s="92"/>
       <c r="C5" s="92"/>
@@ -4366,43 +4369,43 @@
       <c r="L5" s="92"/>
       <c r="M5" s="91"/>
     </row>
-    <row r="6" spans="1:16" ht="22.5" customHeight="1">
+    <row r="6" spans="1:20" ht="22.5" customHeight="1">
       <c r="A6" s="62"/>
-      <c r="B6" s="115" t="s">
+      <c r="B6" s="100" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="104"/>
       <c r="H6" s="89"/>
-      <c r="I6" s="114" t="s">
+      <c r="I6" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="J6" s="114"/>
-      <c r="K6" s="114"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
       <c r="L6" s="89"/>
       <c r="M6" s="88"/>
     </row>
-    <row r="7" spans="1:16" ht="22.5" customHeight="1">
+    <row r="7" spans="1:20" ht="22.5" customHeight="1">
       <c r="A7" s="90"/>
-      <c r="B7" s="116" t="s">
+      <c r="B7" s="101" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="122"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="107"/>
       <c r="H7" s="89"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="114"/>
-      <c r="K7" s="114"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
       <c r="L7" s="89"/>
       <c r="M7" s="88"/>
     </row>
-    <row r="8" spans="1:16" ht="11.25" customHeight="1">
+    <row r="8" spans="1:20" ht="11.25" customHeight="1">
       <c r="A8" s="86"/>
       <c r="B8" s="87"/>
       <c r="C8" s="87"/>
@@ -4417,13 +4420,13 @@
       <c r="L8" s="43"/>
       <c r="M8" s="85"/>
     </row>
-    <row r="9" spans="1:16" ht="22.5" customHeight="1">
+    <row r="9" spans="1:20" ht="22.5" customHeight="1">
       <c r="A9" s="86"/>
-      <c r="B9" s="109" t="s">
+      <c r="B9" s="108" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="109"/>
-      <c r="D9" s="109"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="108"/>
       <c r="E9" s="43"/>
       <c r="F9" s="43"/>
       <c r="G9" s="43"/>
@@ -4434,45 +4437,45 @@
       <c r="L9" s="43"/>
       <c r="M9" s="85"/>
     </row>
-    <row r="10" spans="1:16" ht="22.5" customHeight="1">
+    <row r="10" spans="1:20" ht="22.5" customHeight="1">
       <c r="A10" s="86"/>
-      <c r="B10" s="112" t="s">
+      <c r="B10" s="111" t="s">
         <v>104</v>
       </c>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113"/>
-      <c r="F10" s="113"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="113"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
       <c r="I10" s="43"/>
       <c r="J10" s="43"/>
       <c r="K10" s="43"/>
       <c r="L10" s="43"/>
       <c r="M10" s="85"/>
     </row>
-    <row r="11" spans="1:16" ht="22.5" customHeight="1">
+    <row r="11" spans="1:20" ht="22.5" customHeight="1">
       <c r="A11" s="86"/>
-      <c r="B11" s="112" t="s">
+      <c r="B11" s="111" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="112"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="113"/>
-      <c r="F11" s="113"/>
-      <c r="G11" s="113"/>
-      <c r="H11" s="113"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
       <c r="I11" s="43"/>
       <c r="J11" s="43"/>
       <c r="K11" s="43"/>
       <c r="L11" s="43"/>
       <c r="M11" s="85"/>
     </row>
-    <row r="12" spans="1:16" ht="11.25" customHeight="1">
+    <row r="12" spans="1:20" ht="11.25" customHeight="1">
       <c r="A12" s="62"/>
       <c r="M12" s="60"/>
     </row>
-    <row r="13" spans="1:16" ht="22.5" customHeight="1">
+    <row r="13" spans="1:20" ht="22.5" customHeight="1">
       <c r="A13" s="62"/>
       <c r="B13" s="84" t="s">
         <v>102</v>
@@ -4489,40 +4492,40 @@
       <c r="L13" s="82"/>
       <c r="M13" s="60"/>
     </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1">
+    <row r="14" spans="1:20" ht="15" customHeight="1">
       <c r="A14" s="62"/>
       <c r="B14" s="67"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="108"/>
-      <c r="I14" s="108"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
       <c r="L14" s="66"/>
       <c r="M14" s="60"/>
     </row>
-    <row r="15" spans="1:16" ht="33.75" customHeight="1">
+    <row r="15" spans="1:20" ht="33.75" customHeight="1">
       <c r="A15" s="62"/>
       <c r="B15" s="67"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="101" t="s">
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="113"/>
+      <c r="I15" s="113"/>
+      <c r="J15" s="117" t="s">
         <v>101</v>
       </c>
-      <c r="K15" s="101"/>
-      <c r="L15" s="102"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="118"/>
       <c r="M15" s="78"/>
       <c r="P15" s="42" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="11.25" customHeight="1">
+    <row r="16" spans="1:20" ht="11.25" customHeight="1">
       <c r="A16" s="62"/>
       <c r="B16" s="65"/>
       <c r="C16" s="81"/>
@@ -4560,18 +4563,18 @@
     <row r="18" spans="1:16" ht="36.75" customHeight="1">
       <c r="A18" s="62"/>
       <c r="B18" s="76"/>
-      <c r="C18" s="110" t="s">
+      <c r="C18" s="109" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="111"/>
+      <c r="D18" s="109"/>
+      <c r="E18" s="109"/>
+      <c r="F18" s="109"/>
+      <c r="G18" s="109"/>
+      <c r="H18" s="109"/>
+      <c r="I18" s="109"/>
+      <c r="J18" s="109"/>
+      <c r="K18" s="109"/>
+      <c r="L18" s="110"/>
       <c r="M18" s="75"/>
       <c r="O18" s="74" t="b">
         <v>0</v>
@@ -4583,18 +4586,18 @@
     <row r="19" spans="1:16" ht="36.75" customHeight="1">
       <c r="A19" s="62"/>
       <c r="B19" s="76"/>
-      <c r="C19" s="110" t="s">
+      <c r="C19" s="109" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="111"/>
+      <c r="D19" s="109"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="109"/>
+      <c r="G19" s="109"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="109"/>
+      <c r="J19" s="109"/>
+      <c r="K19" s="109"/>
+      <c r="L19" s="110"/>
       <c r="M19" s="75"/>
       <c r="O19" s="74" t="b">
         <v>0</v>
@@ -4606,18 +4609,18 @@
     <row r="20" spans="1:16" ht="36.75" customHeight="1">
       <c r="A20" s="62"/>
       <c r="B20" s="76"/>
-      <c r="C20" s="110" t="s">
+      <c r="C20" s="109" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="111"/>
+      <c r="D20" s="109"/>
+      <c r="E20" s="109"/>
+      <c r="F20" s="109"/>
+      <c r="G20" s="109"/>
+      <c r="H20" s="109"/>
+      <c r="I20" s="109"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="110"/>
       <c r="M20" s="75"/>
       <c r="O20" s="74" t="b">
         <v>0</v>
@@ -4629,18 +4632,18 @@
     <row r="21" spans="1:16" ht="36.75" customHeight="1">
       <c r="A21" s="62"/>
       <c r="B21" s="76"/>
-      <c r="C21" s="110" t="s">
+      <c r="C21" s="109" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="110"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="110"/>
-      <c r="J21" s="110"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="111"/>
+      <c r="D21" s="109"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="109"/>
+      <c r="G21" s="109"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="110"/>
       <c r="M21" s="75"/>
       <c r="O21" s="74" t="b">
         <v>0</v>
@@ -4652,15 +4655,15 @@
     <row r="22" spans="1:16" ht="15" customHeight="1">
       <c r="A22" s="62"/>
       <c r="B22" s="67"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="103"/>
-      <c r="K22" s="103"/>
-      <c r="L22" s="104"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="120"/>
       <c r="M22" s="60"/>
       <c r="P22" s="42" t="s">
         <v>89</v>
@@ -4668,19 +4671,19 @@
     </row>
     <row r="23" spans="1:16" ht="22.5" customHeight="1">
       <c r="A23" s="62"/>
-      <c r="B23" s="105" t="s">
+      <c r="B23" s="121" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="106"/>
-      <c r="D23" s="106"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="107"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="122"/>
+      <c r="H23" s="122"/>
+      <c r="I23" s="122"/>
+      <c r="J23" s="122"/>
+      <c r="K23" s="122"/>
+      <c r="L23" s="123"/>
       <c r="M23" s="73"/>
       <c r="P23" s="42" t="s">
         <v>87</v>
@@ -4731,9 +4734,9 @@
         <v>83</v>
       </c>
       <c r="H27" s="69"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="100"/>
+      <c r="I27" s="116"/>
+      <c r="J27" s="116"/>
+      <c r="K27" s="116"/>
       <c r="L27" s="66"/>
       <c r="M27" s="60"/>
     </row>
@@ -4743,10 +4746,10 @@
       <c r="C28" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="H28" s="100"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="100"/>
+      <c r="H28" s="116"/>
+      <c r="I28" s="116"/>
+      <c r="J28" s="116"/>
+      <c r="K28" s="116"/>
       <c r="L28" s="66"/>
       <c r="M28" s="60"/>
     </row>
@@ -4762,9 +4765,9 @@
       <c r="G30" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="I30" s="98"/>
-      <c r="J30" s="98"/>
-      <c r="K30" s="98"/>
+      <c r="I30" s="114"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="114"/>
       <c r="L30" s="66"/>
       <c r="M30" s="60"/>
     </row>
@@ -4776,12 +4779,12 @@
     </row>
     <row r="32" spans="1:16" ht="22.5" customHeight="1">
       <c r="A32" s="62"/>
-      <c r="B32" s="99" t="s">
+      <c r="B32" s="115" t="s">
         <v>125</v>
       </c>
-      <c r="C32" s="98"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="98"/>
+      <c r="C32" s="114"/>
+      <c r="D32" s="114"/>
+      <c r="E32" s="114"/>
       <c r="F32" s="42" t="s">
         <v>80</v>
       </c>
@@ -4835,13 +4838,16 @@
       <c r="M36" s="56"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Pv92ZqwUakwYvj90vDXFFtqSF2E1DHXl5hV5K6Dq3lZGD+TQ7CrXrJm2YtXlG9pGZff7sFf1iI8fIDe2E6qmgg==" saltValue="MTiqV5/dyQb5DMWrZA5gxA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FiMbpmbWBeCJPLHqFb2B9gtPuJY94iU+uS5o5arOXTdji0AQvAEi4VLOzybf3nnAgs3ZDljDRvA5d/Ks3C+yKQ==" saltValue="oytv4VqsrpbQQYat5YhiMA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="23">
-    <mergeCell ref="J6:K7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="D22:L22"/>
+    <mergeCell ref="B23:L23"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="I27:K27"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="C18:L18"/>
     <mergeCell ref="C19:L19"/>
@@ -4852,14 +4858,11 @@
     <mergeCell ref="E10:H10"/>
     <mergeCell ref="E11:H11"/>
     <mergeCell ref="C14:I14"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="D22:L22"/>
-    <mergeCell ref="B23:L23"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="J6:K7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="E6:G7"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <dataValidations count="4">
@@ -5006,39 +5009,39 @@
     </row>
     <row r="2" spans="1:54" ht="15" customHeight="1"/>
     <row r="3" spans="1:54" ht="50.1" customHeight="1">
-      <c r="A3" s="125" t="s">
+      <c r="A3" s="128" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="125"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="125"/>
-      <c r="M3" s="125"/>
-      <c r="N3" s="125"/>
-      <c r="O3" s="125"/>
-      <c r="P3" s="125"/>
-      <c r="Q3" s="125"/>
-      <c r="R3" s="125"/>
-      <c r="S3" s="125"/>
-      <c r="T3" s="125"/>
-      <c r="U3" s="125"/>
-      <c r="V3" s="125"/>
-      <c r="W3" s="125"/>
-      <c r="X3" s="125"/>
-      <c r="Y3" s="125"/>
-      <c r="Z3" s="125"/>
-      <c r="AA3" s="125"/>
-      <c r="AB3" s="125"/>
-      <c r="AC3" s="125"/>
-      <c r="AD3" s="125"/>
-      <c r="AE3" s="125"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="128"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
       <c r="AF3" s="7"/>
       <c r="AG3" s="7"/>
       <c r="AH3" s="7"/>
@@ -5316,22 +5319,22 @@
     </row>
     <row r="11" spans="1:54" s="17" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A11" s="16"/>
-      <c r="B11" s="128" t="s">
+      <c r="B11" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="128"/>
-      <c r="D11" s="126"/>
-      <c r="E11" s="126"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
       <c r="F11" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
       <c r="I11" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="126"/>
-      <c r="K11" s="126"/>
+      <c r="J11" s="129"/>
+      <c r="K11" s="129"/>
       <c r="L11" s="16" t="s">
         <v>6</v>
       </c>
@@ -5343,18 +5346,18 @@
       <c r="P11" s="16"/>
       <c r="Q11" s="16"/>
       <c r="R11" s="16"/>
-      <c r="S11" s="127"/>
-      <c r="T11" s="127"/>
-      <c r="U11" s="127"/>
-      <c r="V11" s="127"/>
-      <c r="W11" s="127"/>
-      <c r="X11" s="127"/>
-      <c r="Y11" s="127"/>
-      <c r="Z11" s="127"/>
-      <c r="AA11" s="127"/>
-      <c r="AB11" s="127"/>
-      <c r="AC11" s="127"/>
-      <c r="AD11" s="127"/>
+      <c r="S11" s="130"/>
+      <c r="T11" s="130"/>
+      <c r="U11" s="130"/>
+      <c r="V11" s="130"/>
+      <c r="W11" s="130"/>
+      <c r="X11" s="130"/>
+      <c r="Y11" s="130"/>
+      <c r="Z11" s="130"/>
+      <c r="AA11" s="130"/>
+      <c r="AB11" s="130"/>
+      <c r="AC11" s="130"/>
+      <c r="AD11" s="130"/>
       <c r="AE11" s="16"/>
       <c r="AH11" s="19"/>
       <c r="AR11" s="18"/>
@@ -5446,56 +5449,56 @@
       <c r="A14" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="123" t="s">
+      <c r="B14" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="123"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
-      <c r="F14" s="123"/>
-      <c r="G14" s="123"/>
-      <c r="H14" s="124" t="str">
+      <c r="C14" s="124"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="124"/>
+      <c r="G14" s="124"/>
+      <c r="H14" s="127" t="str">
         <f>IF(別添2!E6=0,"",別添2!E6)</f>
         <v/>
       </c>
-      <c r="I14" s="124"/>
-      <c r="J14" s="124"/>
-      <c r="K14" s="124"/>
-      <c r="L14" s="124"/>
-      <c r="M14" s="124"/>
-      <c r="N14" s="124"/>
-      <c r="O14" s="124"/>
-      <c r="P14" s="124"/>
-      <c r="Q14" s="124"/>
-      <c r="R14" s="124"/>
-      <c r="S14" s="124"/>
-      <c r="T14" s="124"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="127"/>
+      <c r="L14" s="127"/>
+      <c r="M14" s="127"/>
+      <c r="N14" s="127"/>
+      <c r="O14" s="127"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
+      <c r="R14" s="127"/>
+      <c r="S14" s="127"/>
+      <c r="T14" s="127"/>
     </row>
     <row r="15" spans="1:54" ht="30" customHeight="1">
-      <c r="B15" s="123" t="s">
+      <c r="B15" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="123"/>
-      <c r="D15" s="123"/>
-      <c r="E15" s="123"/>
-      <c r="F15" s="123"/>
-      <c r="G15" s="123"/>
-      <c r="H15" s="130" t="str">
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="125" t="str">
         <f>IF(別添2!H28=0,"",別添2!H28)</f>
         <v/>
       </c>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="130"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="130"/>
-      <c r="P15" s="130"/>
-      <c r="Q15" s="130"/>
-      <c r="R15" s="130"/>
-      <c r="S15" s="130"/>
-      <c r="T15" s="130"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
+      <c r="M15" s="125"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="125"/>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="125"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="125"/>
     </row>
     <row r="16" spans="1:54" ht="15" customHeight="1">
       <c r="A16" s="12"/>
@@ -5557,20 +5560,20 @@
     </row>
     <row r="19" spans="1:44" ht="30" customHeight="1">
       <c r="A19" s="12"/>
-      <c r="B19" s="131"/>
-      <c r="C19" s="131"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="131"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="131"/>
-      <c r="I19" s="131"/>
-      <c r="J19" s="131"/>
-      <c r="K19" s="131"/>
-      <c r="L19" s="131"/>
-      <c r="M19" s="131"/>
-      <c r="N19" s="131"/>
-      <c r="O19" s="131"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="126"/>
+      <c r="O19" s="126"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
@@ -5578,20 +5581,20 @@
     </row>
     <row r="20" spans="1:44" ht="30" customHeight="1">
       <c r="A20" s="12"/>
-      <c r="B20" s="131"/>
-      <c r="C20" s="131"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="131"/>
-      <c r="G20" s="131"/>
-      <c r="H20" s="131"/>
-      <c r="I20" s="131"/>
-      <c r="J20" s="131"/>
-      <c r="K20" s="131"/>
-      <c r="L20" s="131"/>
-      <c r="M20" s="131"/>
-      <c r="N20" s="131"/>
-      <c r="O20" s="131"/>
+      <c r="B20" s="126"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="126"/>
+      <c r="H20" s="126"/>
+      <c r="I20" s="126"/>
+      <c r="J20" s="126"/>
+      <c r="K20" s="126"/>
+      <c r="L20" s="126"/>
+      <c r="M20" s="126"/>
+      <c r="N20" s="126"/>
+      <c r="O20" s="126"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
@@ -5599,20 +5602,20 @@
     </row>
     <row r="21" spans="1:44" ht="30" customHeight="1">
       <c r="A21" s="12"/>
-      <c r="B21" s="131"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="131"/>
-      <c r="G21" s="131"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="131"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="131"/>
-      <c r="M21" s="131"/>
-      <c r="N21" s="131"/>
-      <c r="O21" s="131"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="126"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="126"/>
+      <c r="H21" s="126"/>
+      <c r="I21" s="126"/>
+      <c r="J21" s="126"/>
+      <c r="K21" s="126"/>
+      <c r="L21" s="126"/>
+      <c r="M21" s="126"/>
+      <c r="N21" s="126"/>
+      <c r="O21" s="126"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -5620,20 +5623,20 @@
     </row>
     <row r="22" spans="1:44" ht="30" customHeight="1">
       <c r="A22" s="12"/>
-      <c r="B22" s="131"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="131"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="131"/>
-      <c r="I22" s="131"/>
-      <c r="J22" s="131"/>
-      <c r="K22" s="131"/>
-      <c r="L22" s="131"/>
-      <c r="M22" s="131"/>
-      <c r="N22" s="131"/>
-      <c r="O22" s="131"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="126"/>
+      <c r="D22" s="126"/>
+      <c r="E22" s="126"/>
+      <c r="F22" s="126"/>
+      <c r="G22" s="126"/>
+      <c r="H22" s="126"/>
+      <c r="I22" s="126"/>
+      <c r="J22" s="126"/>
+      <c r="K22" s="126"/>
+      <c r="L22" s="126"/>
+      <c r="M22" s="126"/>
+      <c r="N22" s="126"/>
+      <c r="O22" s="126"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -5721,32 +5724,32 @@
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="41"/>
-      <c r="D25" s="129"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="129"/>
-      <c r="G25" s="129"/>
-      <c r="H25" s="129"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="129"/>
-      <c r="K25" s="129"/>
-      <c r="L25" s="129"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="129"/>
-      <c r="O25" s="129"/>
-      <c r="P25" s="129"/>
-      <c r="Q25" s="129"/>
-      <c r="R25" s="129"/>
-      <c r="S25" s="129"/>
-      <c r="T25" s="129"/>
-      <c r="U25" s="129"/>
-      <c r="V25" s="129"/>
-      <c r="W25" s="129"/>
-      <c r="X25" s="129"/>
-      <c r="Y25" s="129"/>
-      <c r="Z25" s="129"/>
-      <c r="AA25" s="129"/>
-      <c r="AB25" s="129"/>
-      <c r="AC25" s="129"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="158"/>
+      <c r="G25" s="158"/>
+      <c r="H25" s="158"/>
+      <c r="I25" s="158"/>
+      <c r="J25" s="158"/>
+      <c r="K25" s="158"/>
+      <c r="L25" s="158"/>
+      <c r="M25" s="158"/>
+      <c r="N25" s="158"/>
+      <c r="O25" s="158"/>
+      <c r="P25" s="158"/>
+      <c r="Q25" s="158"/>
+      <c r="R25" s="158"/>
+      <c r="S25" s="158"/>
+      <c r="T25" s="158"/>
+      <c r="U25" s="158"/>
+      <c r="V25" s="158"/>
+      <c r="W25" s="158"/>
+      <c r="X25" s="158"/>
+      <c r="Y25" s="158"/>
+      <c r="Z25" s="158"/>
+      <c r="AA25" s="158"/>
+      <c r="AB25" s="158"/>
+      <c r="AC25" s="158"/>
       <c r="AD25" s="41"/>
       <c r="AE25" s="47"/>
       <c r="AF25" s="47"/>
@@ -5758,32 +5761,32 @@
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="41"/>
-      <c r="D26" s="129"/>
-      <c r="E26" s="129"/>
-      <c r="F26" s="129"/>
-      <c r="G26" s="129"/>
-      <c r="H26" s="129"/>
-      <c r="I26" s="129"/>
-      <c r="J26" s="129"/>
-      <c r="K26" s="129"/>
-      <c r="L26" s="129"/>
-      <c r="M26" s="129"/>
-      <c r="N26" s="129"/>
-      <c r="O26" s="129"/>
-      <c r="P26" s="129"/>
-      <c r="Q26" s="129"/>
-      <c r="R26" s="129"/>
-      <c r="S26" s="129"/>
-      <c r="T26" s="129"/>
-      <c r="U26" s="129"/>
-      <c r="V26" s="129"/>
-      <c r="W26" s="129"/>
-      <c r="X26" s="129"/>
-      <c r="Y26" s="129"/>
-      <c r="Z26" s="129"/>
-      <c r="AA26" s="129"/>
-      <c r="AB26" s="129"/>
-      <c r="AC26" s="129"/>
+      <c r="D26" s="158"/>
+      <c r="E26" s="158"/>
+      <c r="F26" s="158"/>
+      <c r="G26" s="158"/>
+      <c r="H26" s="158"/>
+      <c r="I26" s="158"/>
+      <c r="J26" s="158"/>
+      <c r="K26" s="158"/>
+      <c r="L26" s="158"/>
+      <c r="M26" s="158"/>
+      <c r="N26" s="158"/>
+      <c r="O26" s="158"/>
+      <c r="P26" s="158"/>
+      <c r="Q26" s="158"/>
+      <c r="R26" s="158"/>
+      <c r="S26" s="158"/>
+      <c r="T26" s="158"/>
+      <c r="U26" s="158"/>
+      <c r="V26" s="158"/>
+      <c r="W26" s="158"/>
+      <c r="X26" s="158"/>
+      <c r="Y26" s="158"/>
+      <c r="Z26" s="158"/>
+      <c r="AA26" s="158"/>
+      <c r="AB26" s="158"/>
+      <c r="AC26" s="158"/>
       <c r="AD26" s="41"/>
       <c r="AE26" s="47"/>
       <c r="AF26" s="47"/>
@@ -5795,32 +5798,32 @@
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="41"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="129"/>
-      <c r="G27" s="129"/>
-      <c r="H27" s="129"/>
-      <c r="I27" s="129"/>
-      <c r="J27" s="129"/>
-      <c r="K27" s="129"/>
-      <c r="L27" s="129"/>
-      <c r="M27" s="129"/>
-      <c r="N27" s="129"/>
-      <c r="O27" s="129"/>
-      <c r="P27" s="129"/>
-      <c r="Q27" s="129"/>
-      <c r="R27" s="129"/>
-      <c r="S27" s="129"/>
-      <c r="T27" s="129"/>
-      <c r="U27" s="129"/>
-      <c r="V27" s="129"/>
-      <c r="W27" s="129"/>
-      <c r="X27" s="129"/>
-      <c r="Y27" s="129"/>
-      <c r="Z27" s="129"/>
-      <c r="AA27" s="129"/>
-      <c r="AB27" s="129"/>
-      <c r="AC27" s="129"/>
+      <c r="D27" s="158"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="158"/>
+      <c r="G27" s="158"/>
+      <c r="H27" s="158"/>
+      <c r="I27" s="158"/>
+      <c r="J27" s="158"/>
+      <c r="K27" s="158"/>
+      <c r="L27" s="158"/>
+      <c r="M27" s="158"/>
+      <c r="N27" s="158"/>
+      <c r="O27" s="158"/>
+      <c r="P27" s="158"/>
+      <c r="Q27" s="158"/>
+      <c r="R27" s="158"/>
+      <c r="S27" s="158"/>
+      <c r="T27" s="158"/>
+      <c r="U27" s="158"/>
+      <c r="V27" s="158"/>
+      <c r="W27" s="158"/>
+      <c r="X27" s="158"/>
+      <c r="Y27" s="158"/>
+      <c r="Z27" s="158"/>
+      <c r="AA27" s="158"/>
+      <c r="AB27" s="158"/>
+      <c r="AC27" s="158"/>
       <c r="AD27" s="41"/>
       <c r="AE27" s="47"/>
       <c r="AF27" s="47"/>
@@ -5832,32 +5835,32 @@
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="41"/>
-      <c r="D28" s="129"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="129"/>
-      <c r="G28" s="129"/>
-      <c r="H28" s="129"/>
-      <c r="I28" s="129"/>
-      <c r="J28" s="129"/>
-      <c r="K28" s="129"/>
-      <c r="L28" s="129"/>
-      <c r="M28" s="129"/>
-      <c r="N28" s="129"/>
-      <c r="O28" s="129"/>
-      <c r="P28" s="129"/>
-      <c r="Q28" s="129"/>
-      <c r="R28" s="129"/>
-      <c r="S28" s="129"/>
-      <c r="T28" s="129"/>
-      <c r="U28" s="129"/>
-      <c r="V28" s="129"/>
-      <c r="W28" s="129"/>
-      <c r="X28" s="129"/>
-      <c r="Y28" s="129"/>
-      <c r="Z28" s="129"/>
-      <c r="AA28" s="129"/>
-      <c r="AB28" s="129"/>
-      <c r="AC28" s="129"/>
+      <c r="D28" s="158"/>
+      <c r="E28" s="158"/>
+      <c r="F28" s="158"/>
+      <c r="G28" s="158"/>
+      <c r="H28" s="158"/>
+      <c r="I28" s="158"/>
+      <c r="J28" s="158"/>
+      <c r="K28" s="158"/>
+      <c r="L28" s="158"/>
+      <c r="M28" s="158"/>
+      <c r="N28" s="158"/>
+      <c r="O28" s="158"/>
+      <c r="P28" s="158"/>
+      <c r="Q28" s="158"/>
+      <c r="R28" s="158"/>
+      <c r="S28" s="158"/>
+      <c r="T28" s="158"/>
+      <c r="U28" s="158"/>
+      <c r="V28" s="158"/>
+      <c r="W28" s="158"/>
+      <c r="X28" s="158"/>
+      <c r="Y28" s="158"/>
+      <c r="Z28" s="158"/>
+      <c r="AA28" s="158"/>
+      <c r="AB28" s="158"/>
+      <c r="AC28" s="158"/>
       <c r="AD28" s="41"/>
       <c r="AE28" s="47"/>
       <c r="AF28" s="47"/>
@@ -5869,32 +5872,32 @@
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="41"/>
-      <c r="D29" s="129"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="129"/>
-      <c r="H29" s="129"/>
-      <c r="I29" s="129"/>
-      <c r="J29" s="129"/>
-      <c r="K29" s="129"/>
-      <c r="L29" s="129"/>
-      <c r="M29" s="129"/>
-      <c r="N29" s="129"/>
-      <c r="O29" s="129"/>
-      <c r="P29" s="129"/>
-      <c r="Q29" s="129"/>
-      <c r="R29" s="129"/>
-      <c r="S29" s="129"/>
-      <c r="T29" s="129"/>
-      <c r="U29" s="129"/>
-      <c r="V29" s="129"/>
-      <c r="W29" s="129"/>
-      <c r="X29" s="129"/>
-      <c r="Y29" s="129"/>
-      <c r="Z29" s="129"/>
-      <c r="AA29" s="129"/>
-      <c r="AB29" s="129"/>
-      <c r="AC29" s="129"/>
+      <c r="D29" s="158"/>
+      <c r="E29" s="158"/>
+      <c r="F29" s="158"/>
+      <c r="G29" s="158"/>
+      <c r="H29" s="158"/>
+      <c r="I29" s="158"/>
+      <c r="J29" s="158"/>
+      <c r="K29" s="158"/>
+      <c r="L29" s="158"/>
+      <c r="M29" s="158"/>
+      <c r="N29" s="158"/>
+      <c r="O29" s="158"/>
+      <c r="P29" s="158"/>
+      <c r="Q29" s="158"/>
+      <c r="R29" s="158"/>
+      <c r="S29" s="158"/>
+      <c r="T29" s="158"/>
+      <c r="U29" s="158"/>
+      <c r="V29" s="158"/>
+      <c r="W29" s="158"/>
+      <c r="X29" s="158"/>
+      <c r="Y29" s="158"/>
+      <c r="Z29" s="158"/>
+      <c r="AA29" s="158"/>
+      <c r="AB29" s="158"/>
+      <c r="AC29" s="158"/>
       <c r="AD29" s="41"/>
       <c r="AE29" s="47"/>
       <c r="AF29" s="47"/>
@@ -5906,32 +5909,32 @@
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
       <c r="C30" s="41"/>
-      <c r="D30" s="129"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="129"/>
-      <c r="G30" s="129"/>
-      <c r="H30" s="129"/>
-      <c r="I30" s="129"/>
-      <c r="J30" s="129"/>
-      <c r="K30" s="129"/>
-      <c r="L30" s="129"/>
-      <c r="M30" s="129"/>
-      <c r="N30" s="129"/>
-      <c r="O30" s="129"/>
-      <c r="P30" s="129"/>
-      <c r="Q30" s="129"/>
-      <c r="R30" s="129"/>
-      <c r="S30" s="129"/>
-      <c r="T30" s="129"/>
-      <c r="U30" s="129"/>
-      <c r="V30" s="129"/>
-      <c r="W30" s="129"/>
-      <c r="X30" s="129"/>
-      <c r="Y30" s="129"/>
-      <c r="Z30" s="129"/>
-      <c r="AA30" s="129"/>
-      <c r="AB30" s="129"/>
-      <c r="AC30" s="129"/>
+      <c r="D30" s="158"/>
+      <c r="E30" s="158"/>
+      <c r="F30" s="158"/>
+      <c r="G30" s="158"/>
+      <c r="H30" s="158"/>
+      <c r="I30" s="158"/>
+      <c r="J30" s="158"/>
+      <c r="K30" s="158"/>
+      <c r="L30" s="158"/>
+      <c r="M30" s="158"/>
+      <c r="N30" s="158"/>
+      <c r="O30" s="158"/>
+      <c r="P30" s="158"/>
+      <c r="Q30" s="158"/>
+      <c r="R30" s="158"/>
+      <c r="S30" s="158"/>
+      <c r="T30" s="158"/>
+      <c r="U30" s="158"/>
+      <c r="V30" s="158"/>
+      <c r="W30" s="158"/>
+      <c r="X30" s="158"/>
+      <c r="Y30" s="158"/>
+      <c r="Z30" s="158"/>
+      <c r="AA30" s="158"/>
+      <c r="AB30" s="158"/>
+      <c r="AC30" s="158"/>
       <c r="AD30" s="41"/>
       <c r="AE30" s="47"/>
       <c r="AF30" s="47"/>
@@ -5943,32 +5946,32 @@
       <c r="A31" s="16"/>
       <c r="B31" s="16"/>
       <c r="C31" s="41"/>
-      <c r="D31" s="129"/>
-      <c r="E31" s="129"/>
-      <c r="F31" s="129"/>
-      <c r="G31" s="129"/>
-      <c r="H31" s="129"/>
-      <c r="I31" s="129"/>
-      <c r="J31" s="129"/>
-      <c r="K31" s="129"/>
-      <c r="L31" s="129"/>
-      <c r="M31" s="129"/>
-      <c r="N31" s="129"/>
-      <c r="O31" s="129"/>
-      <c r="P31" s="129"/>
-      <c r="Q31" s="129"/>
-      <c r="R31" s="129"/>
-      <c r="S31" s="129"/>
-      <c r="T31" s="129"/>
-      <c r="U31" s="129"/>
-      <c r="V31" s="129"/>
-      <c r="W31" s="129"/>
-      <c r="X31" s="129"/>
-      <c r="Y31" s="129"/>
-      <c r="Z31" s="129"/>
-      <c r="AA31" s="129"/>
-      <c r="AB31" s="129"/>
-      <c r="AC31" s="129"/>
+      <c r="D31" s="158"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="158"/>
+      <c r="G31" s="158"/>
+      <c r="H31" s="158"/>
+      <c r="I31" s="158"/>
+      <c r="J31" s="158"/>
+      <c r="K31" s="158"/>
+      <c r="L31" s="158"/>
+      <c r="M31" s="158"/>
+      <c r="N31" s="158"/>
+      <c r="O31" s="158"/>
+      <c r="P31" s="158"/>
+      <c r="Q31" s="158"/>
+      <c r="R31" s="158"/>
+      <c r="S31" s="158"/>
+      <c r="T31" s="158"/>
+      <c r="U31" s="158"/>
+      <c r="V31" s="158"/>
+      <c r="W31" s="158"/>
+      <c r="X31" s="158"/>
+      <c r="Y31" s="158"/>
+      <c r="Z31" s="158"/>
+      <c r="AA31" s="158"/>
+      <c r="AB31" s="158"/>
+      <c r="AC31" s="158"/>
       <c r="AD31" s="41"/>
       <c r="AE31" s="47"/>
       <c r="AF31" s="47"/>
@@ -6054,15 +6057,8 @@
     <row r="54" s="1" customFormat="1" ht="24.95" customHeight="1"/>
     <row r="55" s="1" customFormat="1" ht="24.95" customHeight="1"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Ny/i7ZDCNlBoH7DBANYVISDZi0dTEarOp5QyLi8/gOuHK2lL0nAHUzIKSKJ+olnyM+p2xHfG1TnZEroBOfvXJw==" saltValue="DRMUcCDurEDP0YP6n602CQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kf/EJYGZp4IZgJjxkbjzsW/uHvLAK5FdRPYrPbcOsDO0Mily6uCaVcYTySGYuvpkkDlzQQeFShIBQx80oe1EKA==" saltValue="MC1lN2m34Sd10wuqx4j16A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="15">
-    <mergeCell ref="D25:AC31"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="H15:T15"/>
-    <mergeCell ref="B19:O19"/>
-    <mergeCell ref="B20:O20"/>
-    <mergeCell ref="B21:O21"/>
-    <mergeCell ref="B22:O22"/>
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="H14:T14"/>
     <mergeCell ref="A3:AE3"/>
@@ -6071,6 +6067,13 @@
     <mergeCell ref="J11:K11"/>
     <mergeCell ref="S11:AD11"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D25:AC31"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="H15:T15"/>
+    <mergeCell ref="B19:O19"/>
+    <mergeCell ref="B20:O20"/>
+    <mergeCell ref="B21:O21"/>
+    <mergeCell ref="B22:O22"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <dataValidations count="4">
@@ -6320,43 +6323,43 @@
       <c r="AG1" s="16"/>
     </row>
     <row r="2" spans="1:43" ht="16.149999999999999" customHeight="1">
-      <c r="A2" s="136" t="s">
+      <c r="A2" s="154" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="136"/>
-      <c r="N2" s="136"/>
-      <c r="O2" s="136"/>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="136"/>
-      <c r="R2" s="136"/>
-      <c r="S2" s="136"/>
-      <c r="T2" s="136"/>
-      <c r="U2" s="137"/>
-      <c r="V2" s="137"/>
-      <c r="W2" s="138" t="s">
+      <c r="B2" s="154"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="154"/>
+      <c r="L2" s="154"/>
+      <c r="M2" s="154"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="154"/>
+      <c r="P2" s="154"/>
+      <c r="Q2" s="154"/>
+      <c r="R2" s="154"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="154"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="138"/>
-      <c r="Z2" s="138"/>
-      <c r="AA2" s="138"/>
-      <c r="AB2" s="138"/>
-      <c r="AC2" s="138"/>
-      <c r="AD2" s="138"/>
-      <c r="AE2" s="138"/>
-      <c r="AF2" s="138"/>
-      <c r="AG2" s="138"/>
+      <c r="X2" s="156"/>
+      <c r="Y2" s="156"/>
+      <c r="Z2" s="156"/>
+      <c r="AA2" s="156"/>
+      <c r="AB2" s="156"/>
+      <c r="AC2" s="156"/>
+      <c r="AD2" s="156"/>
+      <c r="AE2" s="156"/>
+      <c r="AF2" s="156"/>
+      <c r="AG2" s="156"/>
     </row>
     <row r="3" spans="1:43" ht="7.15" customHeight="1">
       <c r="A3" s="16"/>
@@ -6412,26 +6415,26 @@
       <c r="P4" s="16"/>
       <c r="Q4" s="16"/>
       <c r="R4" s="16"/>
-      <c r="S4" s="139" t="s">
+      <c r="S4" s="157" t="s">
         <v>22</v>
       </c>
-      <c r="T4" s="139"/>
-      <c r="U4" s="139"/>
-      <c r="V4" s="139"/>
-      <c r="W4" s="139"/>
-      <c r="X4" s="133" t="str">
+      <c r="T4" s="157"/>
+      <c r="U4" s="157"/>
+      <c r="V4" s="157"/>
+      <c r="W4" s="157"/>
+      <c r="X4" s="151" t="str">
         <f>IF(様式101_歯科技工所ベースアップ支援料!H14=0,"",様式101_歯科技工所ベースアップ支援料!H14)</f>
         <v/>
       </c>
-      <c r="Y4" s="134"/>
-      <c r="Z4" s="134"/>
-      <c r="AA4" s="134"/>
-      <c r="AB4" s="134"/>
-      <c r="AC4" s="134"/>
-      <c r="AD4" s="134"/>
-      <c r="AE4" s="134"/>
-      <c r="AF4" s="134"/>
-      <c r="AG4" s="135"/>
+      <c r="Y4" s="152"/>
+      <c r="Z4" s="152"/>
+      <c r="AA4" s="152"/>
+      <c r="AB4" s="152"/>
+      <c r="AC4" s="152"/>
+      <c r="AD4" s="152"/>
+      <c r="AE4" s="152"/>
+      <c r="AF4" s="152"/>
+      <c r="AG4" s="153"/>
     </row>
     <row r="5" spans="1:43" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="16"/>
@@ -6452,26 +6455,26 @@
       <c r="P5" s="16"/>
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
-      <c r="S5" s="128" t="s">
+      <c r="S5" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="T5" s="128"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="128"/>
-      <c r="W5" s="132"/>
-      <c r="X5" s="133" t="str">
+      <c r="T5" s="131"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="131"/>
+      <c r="W5" s="150"/>
+      <c r="X5" s="151" t="str">
         <f>IF(様式101_歯科技工所ベースアップ支援料!H15=0,"",様式101_歯科技工所ベースアップ支援料!H15)</f>
         <v/>
       </c>
-      <c r="Y5" s="134"/>
-      <c r="Z5" s="134"/>
-      <c r="AA5" s="134"/>
-      <c r="AB5" s="134"/>
-      <c r="AC5" s="134"/>
-      <c r="AD5" s="134"/>
-      <c r="AE5" s="134"/>
-      <c r="AF5" s="134"/>
-      <c r="AG5" s="135"/>
+      <c r="Y5" s="152"/>
+      <c r="Z5" s="152"/>
+      <c r="AA5" s="152"/>
+      <c r="AB5" s="152"/>
+      <c r="AC5" s="152"/>
+      <c r="AD5" s="152"/>
+      <c r="AE5" s="152"/>
+      <c r="AF5" s="152"/>
+      <c r="AG5" s="153"/>
     </row>
     <row r="6" spans="1:43" s="24" customFormat="1" ht="16.149999999999999" customHeight="1">
       <c r="X6" s="25"/>
@@ -6648,18 +6651,18 @@
       <c r="AG13" s="16"/>
     </row>
     <row r="14" spans="1:43" ht="16.149999999999999" customHeight="1" thickBot="1">
-      <c r="B14" s="142" t="s">
+      <c r="B14" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="143"/>
-      <c r="D14" s="143"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
+      <c r="C14" s="146"/>
+      <c r="D14" s="146"/>
+      <c r="E14" s="147"/>
+      <c r="F14" s="147"/>
       <c r="G14" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
+      <c r="H14" s="147"/>
+      <c r="I14" s="147"/>
       <c r="J14" s="30" t="s">
         <v>5</v>
       </c>
@@ -6671,23 +6674,23 @@
         <v>28</v>
       </c>
       <c r="N14" s="30"/>
-      <c r="O14" s="144"/>
-      <c r="P14" s="144"/>
+      <c r="O14" s="147"/>
+      <c r="P14" s="147"/>
       <c r="Q14" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="144"/>
-      <c r="S14" s="144"/>
+      <c r="R14" s="147"/>
+      <c r="S14" s="147"/>
       <c r="T14" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="V14" s="140" t="str">
+      <c r="V14" s="148" t="str">
         <f>IF(OR(E14="",H14="",O14="",R14=""),"",((O14-E14)*12)+(R14-H14)+1)</f>
         <v/>
       </c>
-      <c r="W14" s="140"/>
-      <c r="X14" s="140"/>
-      <c r="Y14" s="141"/>
+      <c r="W14" s="148"/>
+      <c r="X14" s="148"/>
+      <c r="Y14" s="149"/>
       <c r="Z14" s="16" t="s">
         <v>30</v>
       </c>
@@ -6758,18 +6761,18 @@
     </row>
     <row r="17" spans="1:44" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="A17" s="16"/>
-      <c r="B17" s="142" t="s">
+      <c r="B17" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="143"/>
-      <c r="D17" s="143"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="144"/>
+      <c r="C17" s="146"/>
+      <c r="D17" s="146"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="147"/>
       <c r="G17" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="144"/>
-      <c r="I17" s="144"/>
+      <c r="H17" s="147"/>
+      <c r="I17" s="147"/>
       <c r="J17" s="30" t="s">
         <v>5</v>
       </c>
@@ -6781,23 +6784,23 @@
         <v>28</v>
       </c>
       <c r="N17" s="30"/>
-      <c r="O17" s="144"/>
-      <c r="P17" s="144"/>
+      <c r="O17" s="147"/>
+      <c r="P17" s="147"/>
       <c r="Q17" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
+      <c r="R17" s="147"/>
+      <c r="S17" s="147"/>
       <c r="T17" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="V17" s="140" t="str">
+      <c r="V17" s="148" t="str">
         <f>IF(OR(E17="",H17="",O17="",R17=""),"",((O17-E17)*12)+(R17-H17)+1)</f>
         <v/>
       </c>
-      <c r="W17" s="140"/>
-      <c r="X17" s="140"/>
-      <c r="Y17" s="141"/>
+      <c r="W17" s="148"/>
+      <c r="X17" s="148"/>
+      <c r="Y17" s="149"/>
       <c r="Z17" s="16" t="s">
         <v>30</v>
       </c>
@@ -6934,12 +6937,12 @@
       <c r="Q21" s="16"/>
       <c r="R21" s="16"/>
       <c r="S21" s="16"/>
-      <c r="T21" s="151"/>
-      <c r="U21" s="151"/>
-      <c r="V21" s="151"/>
-      <c r="W21" s="151"/>
-      <c r="X21" s="151"/>
-      <c r="Y21" s="151"/>
+      <c r="T21" s="140"/>
+      <c r="U21" s="140"/>
+      <c r="V21" s="140"/>
+      <c r="W21" s="140"/>
+      <c r="X21" s="140"/>
+      <c r="Y21" s="140"/>
       <c r="Z21" s="16"/>
       <c r="AA21" s="16"/>
       <c r="AB21" s="16"/>
@@ -6980,14 +6983,14 @@
       <c r="Y22" s="36"/>
       <c r="Z22" s="36"/>
       <c r="AA22" s="36"/>
-      <c r="AB22" s="152">
+      <c r="AB22" s="141">
         <f>SUM(P28,P29,P30,P31)</f>
         <v>0</v>
       </c>
-      <c r="AC22" s="152"/>
-      <c r="AD22" s="152"/>
-      <c r="AE22" s="152"/>
-      <c r="AF22" s="152"/>
+      <c r="AC22" s="141"/>
+      <c r="AD22" s="141"/>
+      <c r="AE22" s="141"/>
+      <c r="AF22" s="141"/>
       <c r="AG22" s="37" t="s">
         <v>34</v>
       </c>
@@ -7023,14 +7026,14 @@
       <c r="Y23" s="50"/>
       <c r="Z23" s="50"/>
       <c r="AA23" s="50"/>
-      <c r="AB23" s="153">
+      <c r="AB23" s="142">
         <f>AB22*150</f>
         <v>0</v>
       </c>
-      <c r="AC23" s="153"/>
-      <c r="AD23" s="153"/>
-      <c r="AE23" s="153"/>
-      <c r="AF23" s="153"/>
+      <c r="AC23" s="142"/>
+      <c r="AD23" s="142"/>
+      <c r="AE23" s="142"/>
+      <c r="AF23" s="142"/>
       <c r="AG23" s="51" t="s">
         <v>42</v>
       </c>
@@ -7144,27 +7147,27 @@
     </row>
     <row r="27" spans="1:44" ht="15" customHeight="1">
       <c r="A27" s="27"/>
-      <c r="B27" s="154" t="s">
+      <c r="B27" s="143" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="154"/>
-      <c r="D27" s="154"/>
-      <c r="E27" s="154"/>
-      <c r="F27" s="154"/>
-      <c r="G27" s="154"/>
-      <c r="H27" s="154"/>
-      <c r="I27" s="154"/>
-      <c r="J27" s="154"/>
-      <c r="K27" s="154"/>
-      <c r="L27" s="154"/>
-      <c r="M27" s="154"/>
-      <c r="N27" s="154"/>
-      <c r="O27" s="155"/>
-      <c r="P27" s="155" t="s">
+      <c r="C27" s="143"/>
+      <c r="D27" s="143"/>
+      <c r="E27" s="143"/>
+      <c r="F27" s="143"/>
+      <c r="G27" s="143"/>
+      <c r="H27" s="143"/>
+      <c r="I27" s="143"/>
+      <c r="J27" s="143"/>
+      <c r="K27" s="143"/>
+      <c r="L27" s="143"/>
+      <c r="M27" s="143"/>
+      <c r="N27" s="143"/>
+      <c r="O27" s="144"/>
+      <c r="P27" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="Q27" s="155"/>
-      <c r="R27" s="155"/>
+      <c r="Q27" s="144"/>
+      <c r="R27" s="144"/>
       <c r="S27" s="16"/>
       <c r="T27" s="16"/>
       <c r="U27" s="16"/>
@@ -7183,23 +7186,23 @@
     </row>
     <row r="28" spans="1:44" ht="15" customHeight="1">
       <c r="A28" s="27"/>
-      <c r="B28" s="145"/>
-      <c r="C28" s="146"/>
-      <c r="D28" s="146"/>
-      <c r="E28" s="146"/>
-      <c r="F28" s="146"/>
-      <c r="G28" s="146"/>
-      <c r="H28" s="146"/>
-      <c r="I28" s="146"/>
-      <c r="J28" s="146"/>
-      <c r="K28" s="146"/>
-      <c r="L28" s="146"/>
-      <c r="M28" s="146"/>
-      <c r="N28" s="147"/>
+      <c r="B28" s="134"/>
+      <c r="C28" s="135"/>
+      <c r="D28" s="135"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="135"/>
+      <c r="G28" s="135"/>
+      <c r="H28" s="135"/>
+      <c r="I28" s="135"/>
+      <c r="J28" s="135"/>
+      <c r="K28" s="135"/>
+      <c r="L28" s="135"/>
+      <c r="M28" s="135"/>
+      <c r="N28" s="136"/>
       <c r="O28" s="44"/>
-      <c r="P28" s="148"/>
-      <c r="Q28" s="149"/>
-      <c r="R28" s="150"/>
+      <c r="P28" s="137"/>
+      <c r="Q28" s="138"/>
+      <c r="R28" s="139"/>
       <c r="S28" s="16" t="s">
         <v>34</v>
       </c>
@@ -7220,23 +7223,23 @@
     </row>
     <row r="29" spans="1:44" ht="15" customHeight="1">
       <c r="A29" s="27"/>
-      <c r="B29" s="145"/>
-      <c r="C29" s="146"/>
-      <c r="D29" s="146"/>
-      <c r="E29" s="146"/>
-      <c r="F29" s="146"/>
-      <c r="G29" s="146"/>
-      <c r="H29" s="146"/>
-      <c r="I29" s="146"/>
-      <c r="J29" s="146"/>
-      <c r="K29" s="146"/>
-      <c r="L29" s="146"/>
-      <c r="M29" s="146"/>
-      <c r="N29" s="147"/>
+      <c r="B29" s="134"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="135"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="135"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="135"/>
+      <c r="I29" s="135"/>
+      <c r="J29" s="135"/>
+      <c r="K29" s="135"/>
+      <c r="L29" s="135"/>
+      <c r="M29" s="135"/>
+      <c r="N29" s="136"/>
       <c r="O29" s="44"/>
-      <c r="P29" s="148"/>
-      <c r="Q29" s="149"/>
-      <c r="R29" s="150"/>
+      <c r="P29" s="137"/>
+      <c r="Q29" s="138"/>
+      <c r="R29" s="139"/>
       <c r="S29" s="16" t="s">
         <v>34</v>
       </c>
@@ -7257,23 +7260,23 @@
     </row>
     <row r="30" spans="1:44" ht="15" customHeight="1">
       <c r="A30" s="27"/>
-      <c r="B30" s="145"/>
-      <c r="C30" s="146"/>
-      <c r="D30" s="146"/>
-      <c r="E30" s="146"/>
-      <c r="F30" s="146"/>
-      <c r="G30" s="146"/>
-      <c r="H30" s="146"/>
-      <c r="I30" s="146"/>
-      <c r="J30" s="146"/>
-      <c r="K30" s="146"/>
-      <c r="L30" s="146"/>
-      <c r="M30" s="146"/>
-      <c r="N30" s="147"/>
+      <c r="B30" s="134"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="135"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="135"/>
+      <c r="J30" s="135"/>
+      <c r="K30" s="135"/>
+      <c r="L30" s="135"/>
+      <c r="M30" s="135"/>
+      <c r="N30" s="136"/>
       <c r="O30" s="44"/>
-      <c r="P30" s="148"/>
-      <c r="Q30" s="149"/>
-      <c r="R30" s="150"/>
+      <c r="P30" s="137"/>
+      <c r="Q30" s="138"/>
+      <c r="R30" s="139"/>
       <c r="S30" s="16" t="s">
         <v>34</v>
       </c>
@@ -7294,23 +7297,23 @@
     </row>
     <row r="31" spans="1:44" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
-      <c r="B31" s="145"/>
-      <c r="C31" s="146"/>
-      <c r="D31" s="146"/>
-      <c r="E31" s="146"/>
-      <c r="F31" s="146"/>
-      <c r="G31" s="146"/>
-      <c r="H31" s="146"/>
-      <c r="I31" s="146"/>
-      <c r="J31" s="146"/>
-      <c r="K31" s="146"/>
-      <c r="L31" s="146"/>
-      <c r="M31" s="146"/>
-      <c r="N31" s="147"/>
+      <c r="B31" s="134"/>
+      <c r="C31" s="135"/>
+      <c r="D31" s="135"/>
+      <c r="E31" s="135"/>
+      <c r="F31" s="135"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="135"/>
+      <c r="I31" s="135"/>
+      <c r="J31" s="135"/>
+      <c r="K31" s="135"/>
+      <c r="L31" s="135"/>
+      <c r="M31" s="135"/>
+      <c r="N31" s="136"/>
       <c r="O31" s="44"/>
-      <c r="P31" s="148"/>
-      <c r="Q31" s="149"/>
-      <c r="R31" s="150"/>
+      <c r="P31" s="137"/>
+      <c r="Q31" s="138"/>
+      <c r="R31" s="139"/>
       <c r="S31" s="16" t="s">
         <v>34</v>
       </c>
@@ -7519,18 +7522,18 @@
         <v>28</v>
       </c>
       <c r="E37" s="16"/>
-      <c r="F37" s="126"/>
-      <c r="G37" s="126"/>
+      <c r="F37" s="129"/>
+      <c r="G37" s="129"/>
       <c r="H37" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I37" s="126"/>
-      <c r="J37" s="126"/>
+      <c r="I37" s="129"/>
+      <c r="J37" s="129"/>
       <c r="K37" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L37" s="126"/>
-      <c r="M37" s="126"/>
+      <c r="L37" s="129"/>
+      <c r="M37" s="129"/>
       <c r="N37" s="16" t="s">
         <v>6</v>
       </c>
@@ -7542,21 +7545,21 @@
       <c r="R37" s="16"/>
       <c r="S37" s="16"/>
       <c r="T37" s="16"/>
-      <c r="U37" s="156" t="str">
+      <c r="U37" s="132" t="str">
         <f>IF(様式101_歯科技工所ベースアップ支援料!S11=0,"",様式101_歯科技工所ベースアップ支援料!S11)</f>
         <v/>
       </c>
-      <c r="V37" s="156"/>
-      <c r="W37" s="156"/>
-      <c r="X37" s="156"/>
-      <c r="Y37" s="156"/>
-      <c r="Z37" s="156"/>
-      <c r="AA37" s="156"/>
-      <c r="AB37" s="156"/>
-      <c r="AC37" s="156"/>
-      <c r="AD37" s="156"/>
-      <c r="AE37" s="156"/>
-      <c r="AF37" s="156"/>
+      <c r="V37" s="132"/>
+      <c r="W37" s="132"/>
+      <c r="X37" s="132"/>
+      <c r="Y37" s="132"/>
+      <c r="Z37" s="132"/>
+      <c r="AA37" s="132"/>
+      <c r="AB37" s="132"/>
+      <c r="AC37" s="132"/>
+      <c r="AD37" s="132"/>
+      <c r="AE37" s="132"/>
+      <c r="AF37" s="132"/>
       <c r="AG37" s="16"/>
       <c r="AH37" s="19"/>
       <c r="AR37" s="18"/>
@@ -7712,41 +7715,41 @@
       <c r="AR41" s="18"/>
     </row>
     <row r="42" spans="1:44" s="17" customFormat="1" ht="15" customHeight="1">
-      <c r="A42" s="157" t="s">
+      <c r="A42" s="133" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="157"/>
-      <c r="C42" s="157"/>
-      <c r="D42" s="157"/>
-      <c r="E42" s="157"/>
-      <c r="F42" s="157"/>
-      <c r="G42" s="157"/>
-      <c r="H42" s="157"/>
-      <c r="I42" s="157"/>
-      <c r="J42" s="157"/>
-      <c r="K42" s="157"/>
-      <c r="L42" s="157"/>
-      <c r="M42" s="157"/>
-      <c r="N42" s="157"/>
-      <c r="O42" s="157"/>
-      <c r="P42" s="157"/>
-      <c r="Q42" s="157"/>
-      <c r="R42" s="157"/>
-      <c r="S42" s="157"/>
-      <c r="T42" s="157"/>
-      <c r="U42" s="157"/>
-      <c r="V42" s="157"/>
-      <c r="W42" s="157"/>
-      <c r="X42" s="157"/>
-      <c r="Y42" s="157"/>
-      <c r="Z42" s="157"/>
-      <c r="AA42" s="157"/>
-      <c r="AB42" s="157"/>
-      <c r="AC42" s="157"/>
-      <c r="AD42" s="157"/>
-      <c r="AE42" s="157"/>
-      <c r="AF42" s="157"/>
-      <c r="AG42" s="157"/>
+      <c r="B42" s="133"/>
+      <c r="C42" s="133"/>
+      <c r="D42" s="133"/>
+      <c r="E42" s="133"/>
+      <c r="F42" s="133"/>
+      <c r="G42" s="133"/>
+      <c r="H42" s="133"/>
+      <c r="I42" s="133"/>
+      <c r="J42" s="133"/>
+      <c r="K42" s="133"/>
+      <c r="L42" s="133"/>
+      <c r="M42" s="133"/>
+      <c r="N42" s="133"/>
+      <c r="O42" s="133"/>
+      <c r="P42" s="133"/>
+      <c r="Q42" s="133"/>
+      <c r="R42" s="133"/>
+      <c r="S42" s="133"/>
+      <c r="T42" s="133"/>
+      <c r="U42" s="133"/>
+      <c r="V42" s="133"/>
+      <c r="W42" s="133"/>
+      <c r="X42" s="133"/>
+      <c r="Y42" s="133"/>
+      <c r="Z42" s="133"/>
+      <c r="AA42" s="133"/>
+      <c r="AB42" s="133"/>
+      <c r="AC42" s="133"/>
+      <c r="AD42" s="133"/>
+      <c r="AE42" s="133"/>
+      <c r="AF42" s="133"/>
+      <c r="AG42" s="133"/>
       <c r="AH42" s="19"/>
       <c r="AR42" s="18"/>
     </row>
@@ -8797,22 +8800,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="e2xfTlOIWo0jLfWpqg3IMx7ugoZzjHgv0oQ9r/lDfwOrJrNvfkeSEbonYRMQG1EIGk/0Ctdgop3gpm+15kJXJA==" saltValue="ZgrCNmqz5mF3cnmxeWheSg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="37">
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="U37:AF37"/>
-    <mergeCell ref="A42:AG42"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="P29:R29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="P30:R30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="P31:R31"/>
-    <mergeCell ref="T21:Y21"/>
-    <mergeCell ref="AB22:AF22"/>
-    <mergeCell ref="AB23:AF23"/>
-    <mergeCell ref="B27:O27"/>
-    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="S5:W5"/>
+    <mergeCell ref="X5:AG5"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:AG2"/>
+    <mergeCell ref="S4:W4"/>
+    <mergeCell ref="X4:AG4"/>
+    <mergeCell ref="V17:Y17"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="V14:Y14"/>
     <mergeCell ref="B28:N28"/>
     <mergeCell ref="P28:R28"/>
     <mergeCell ref="B17:D17"/>
@@ -8820,20 +8821,22 @@
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="O17:P17"/>
     <mergeCell ref="R17:S17"/>
-    <mergeCell ref="V17:Y17"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="V14:Y14"/>
-    <mergeCell ref="S5:W5"/>
-    <mergeCell ref="X5:AG5"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:AG2"/>
-    <mergeCell ref="S4:W4"/>
-    <mergeCell ref="X4:AG4"/>
+    <mergeCell ref="T21:Y21"/>
+    <mergeCell ref="AB22:AF22"/>
+    <mergeCell ref="AB23:AF23"/>
+    <mergeCell ref="B27:O27"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="P29:R29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="P30:R30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="P31:R31"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="U37:AF37"/>
+    <mergeCell ref="A42:AG42"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <dataValidations count="3">
@@ -9028,7 +9031,7 @@
       <c r="A2" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="158">
+      <c r="B2" s="98">
         <f>別添2!$E$6</f>
         <v>0</v>
       </c>
@@ -9214,29 +9217,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A14803322066C74F9BE02317CD0CDCCD" ma:contentTypeVersion="125" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c4d0cbc5c65bf0286e4b5d882495989e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7416dcb5-151a-428d-b9dd-c50cd68ce8a8" xmlns:ns3="cc65c493-46e3-4a51-bdc3-517cdfaa7574" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="10bb90dc8f083b7d0038c94280cbf4fb" ns2:_="" ns3:_="">
-    <xsd:import namespace="7416dcb5-151a-428d-b9dd-c50cd68ce8a8"/>
-    <xsd:import namespace="cc65c493-46e3-4a51-bdc3-517cdfaa7574"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100DEA2635F732F464D88FD0617849E9F69" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="07a4d2faf2f8f28b7a2f551c9ec83f9e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="33f003c0-0d95-44a8-96ef-b6b435aaba2f" xmlns:ns3="263dbbe5-076b-4606-a03b-9598f5f2f35a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8a3684643123949165adbe6bede2192a" ns2:_="" ns3:_="">
+    <xsd:import namespace="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
+    <xsd:import namespace="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
+                <xsd:element ref="ns2:Owner" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -9244,74 +9248,13 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7416dcb5-151a-428d-b9dd-c50cd68ce8a8" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="33f003c0-0d95-44a8-96ef-b6b435aaba2f" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="16" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="17" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="19" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:displayName="画像タグ_0" ma:hidden="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cc65c493-46e3-4a51-bdc3-517cdfaa7574" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="共有相手" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="Owner" ma:index="8" nillable="true" ma:displayName="所有者" ma:internalName="Owner">
       <xsd:complexType>
         <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
+          <xsd:extension base="dms:User">
             <xsd:sequence>
               <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
                 <xsd:complexType>
@@ -9327,12 +9270,84 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="共有相手の詳細情報" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0347f584-7be2-4218-8e94-402d99aedf0b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="22" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="263dbbe5-076b-4606-a03b-9598f5f2f35a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{6c0e5604-1e4d-437b-a747-9a4cb561c167}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="263dbbe5-076b-4606-a03b-9598f5f2f35a">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -9435,6 +9450,24 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="33f003c0-0d95-44a8-96ef-b6b435aaba2f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
+    <Owner xmlns="33f003c0-0d95-44a8-96ef-b6b435aaba2f">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -9443,39 +9476,46 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7416dcb5-151a-428d-b9dd-c50cd68ce8a8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{408D35DF-40B8-4501-B0DD-8B587AA74C23}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D999F158-11CF-4FAB-A637-03A2A5FEB2D5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
+    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3582D205-478C-4C30-B06B-C9C1A6419D04}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62F47F27-459E-4674-83E3-4221F595AD6D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3582D205-478C-4C30-B06B-C9C1A6419D04}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
-    <ds:schemaRef ds:uri="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>